--- a/tests/regression_artifacts/downloads/email_03152025_Free_returns_within_90_days/current/HAWB9600432.xlsx
+++ b/tests/regression_artifacts/downloads/email_03152025_Free_returns_within_90_days/current/HAWB9600432.xlsx
@@ -2217,7 +2217,7 @@
       </c>
       <c r="F36" s="21" t="inlineStr">
         <is>
-          <t>64031900</t>
+          <t>64041990</t>
         </is>
       </c>
       <c r="G36" s="21" t="n"/>
